--- a/spreadsheets/domains/cramps-mat_CRAMPS-MAT_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-mat_CRAMPS-MAT_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R6657305f4f5447c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="Re5c0d08f3c934e6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Ra2e7bc4083114577"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R7138a36d2c2d4423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="Rf34982bf6b6148b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R8da95eab3a4d4479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R5504d6508aa44a44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Rb9b79a3489a64b59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R16202c3c38714e52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="Reacda53936914385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="Rbcb44546957641f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R27a26e1fe4e641b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rcbcaf4d2c86a439d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R3dfb71591da64e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="Re126c78f28074b56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="Rcac2afc97779418f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R49a25f734c42499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R2d20c88eba0e410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R9ee5b84a514b4ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R16d521b9060645e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>unreported failed syntheses; hidden processing parameters; batch variation; simulation convergence artifacts</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
